--- a/Analysis/Sensitivity_merec_entropy_arms_gptoss.xlsx
+++ b/Analysis/Sensitivity_merec_entropy_arms_gptoss.xlsx
@@ -481,7 +481,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.138244, "environmental": 0.127688, "comfort": 0.662899, "practicality": 0.071169}, "Appliance": {"energy_cost": 0.207971, "environmental": 0.043979, "comfort": 0.29187, "practicality": 0.45618}, "Shower": {"energy_cost": 0.250328, "environmental": 0.246522, "comfort": 0.196918, "practicality": 0.306231}}</t>
+          <t>{"HVAC": {"energy_cost": 0.138244, "environmental": 0.127688, "comfort": 0.662899, "practicality": 0.071169}, "Appliance": {"energy_cost": 0.207971, "environmental": 0.043979, "comfort": 0.29187, "practicality": 0.45618}, "Shower": {"energy_cost": 0.250786, "environmental": 0.245387, "comfort": 0.20345, "practicality": 0.300377}}</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -490,22 +490,22 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.16168</v>
+        <v>0.16306</v>
       </c>
       <c r="F2" t="n">
-        <v>0.18358</v>
+        <v>0.18512</v>
       </c>
       <c r="G2" t="n">
-        <v>0.41434</v>
+        <v>0.41536</v>
       </c>
       <c r="H2" t="n">
-        <v>0.74154</v>
+        <v>0.74256</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2249800000000001</v>
+        <v>0.20856</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9075599999999999</v>
+        <v>0.8997999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -521,7 +521,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.138244, "environmental": 0.127688, "comfort": 0.662899, "practicality": 0.071169}, "Appliance": {"energy_cost": 0.207971, "environmental": 0.043979, "comfort": 0.29187, "practicality": 0.45618}, "Shower": {"energy_cost": 0.250328, "environmental": 0.246522, "comfort": 0.196918, "practicality": 0.306231}}</t>
+          <t>{"HVAC": {"energy_cost": 0.138244, "environmental": 0.127688, "comfort": 0.662899, "practicality": 0.071169}, "Appliance": {"energy_cost": 0.207971, "environmental": 0.043979, "comfort": 0.29187, "practicality": 0.45618}, "Shower": {"energy_cost": 0.250786, "environmental": 0.245387, "comfort": 0.20345, "practicality": 0.300377}}</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -530,22 +530,22 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.3866600000000001</v>
+        <v>0.37162</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4097399999999999</v>
+        <v>0.39332</v>
       </c>
       <c r="G3" t="n">
-        <v>0.57128</v>
+        <v>0.57026</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8348799999999998</v>
+        <v>0.8276999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2249800000000001</v>
+        <v>0.20856</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9075599999999999</v>
+        <v>0.8997999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -561,7 +561,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.138244, "environmental": 0.127688, "comfort": 0.662899, "practicality": 0.071169}, "Appliance": {"energy_cost": 0.207971, "environmental": 0.043979, "comfort": 0.29187, "practicality": 0.45618}, "Shower": {"energy_cost": 0.250328, "environmental": 0.246522, "comfort": 0.196918, "practicality": 0.306231}}</t>
+          <t>{"HVAC": {"energy_cost": 0.138244, "environmental": 0.127688, "comfort": 0.662899, "practicality": 0.071169}, "Appliance": {"energy_cost": 0.207971, "environmental": 0.043979, "comfort": 0.29187, "practicality": 0.45618}, "Shower": {"energy_cost": 0.250786, "environmental": 0.245387, "comfort": 0.20345, "practicality": 0.300377}}</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -570,22 +570,22 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.9075599999999999</v>
+        <v>0.8997999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9219200000000001</v>
+        <v>0.91608</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9277599999999999</v>
+        <v>0.9231</v>
       </c>
       <c r="H4" t="n">
         <v>0.9836599999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2249800000000001</v>
+        <v>0.20856</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9075599999999999</v>
+        <v>0.8997999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -601,7 +601,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.336451, "environmental": 0.32038, "comfort": 0.269486, "practicality": 0.073683}, "Appliance": {"energy_cost": 0.193182, "environmental": 0.465156, "comfort": 0.123615, "practicality": 0.218047}, "Shower": {"energy_cost": 0.336687, "environmental": 0.316863, "comfort": 0.118531, "practicality": 0.22792}}</t>
+          <t>{"HVAC": {"energy_cost": 0.336451, "environmental": 0.32038, "comfort": 0.269486, "practicality": 0.073683}, "Appliance": {"energy_cost": 0.193182, "environmental": 0.465156, "comfort": 0.123615, "practicality": 0.218047}, "Shower": {"energy_cost": 0.335356, "environmental": 0.315611, "comfort": 0.122014, "practicality": 0.227019}}</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -610,22 +610,22 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.03932</v>
+        <v>0.04274</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0364</v>
+        <v>0.03948</v>
       </c>
       <c r="G5" t="n">
-        <v>0.34562</v>
+        <v>0.3477</v>
       </c>
       <c r="H5" t="n">
-        <v>0.67284</v>
+        <v>0.6769400000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>0.23452</v>
+        <v>0.2393</v>
       </c>
       <c r="J5" t="n">
-        <v>0.88422</v>
+        <v>0.88812</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.336451, "environmental": 0.32038, "comfort": 0.269486, "practicality": 0.073683}, "Appliance": {"energy_cost": 0.193182, "environmental": 0.465156, "comfort": 0.123615, "practicality": 0.218047}, "Shower": {"energy_cost": 0.336687, "environmental": 0.316863, "comfort": 0.118531, "practicality": 0.22792}}</t>
+          <t>{"HVAC": {"energy_cost": 0.336451, "environmental": 0.32038, "comfort": 0.269486, "practicality": 0.073683}, "Appliance": {"energy_cost": 0.193182, "environmental": 0.465156, "comfort": 0.123615, "practicality": 0.218047}, "Shower": {"energy_cost": 0.335356, "environmental": 0.315611, "comfort": 0.122014, "practicality": 0.227019}}</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -650,22 +650,22 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.27384</v>
+        <v>0.28204</v>
       </c>
       <c r="F6" t="n">
-        <v>0.28566</v>
+        <v>0.29128</v>
       </c>
       <c r="G6" t="n">
-        <v>0.49024</v>
+        <v>0.4964200000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>0.77846</v>
+        <v>0.77128</v>
       </c>
       <c r="I6" t="n">
-        <v>0.23452</v>
+        <v>0.2393</v>
       </c>
       <c r="J6" t="n">
-        <v>0.88422</v>
+        <v>0.88812</v>
       </c>
     </row>
     <row r="7">
@@ -681,7 +681,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.336451, "environmental": 0.32038, "comfort": 0.269486, "practicality": 0.073683}, "Appliance": {"energy_cost": 0.193182, "environmental": 0.465156, "comfort": 0.123615, "practicality": 0.218047}, "Shower": {"energy_cost": 0.336687, "environmental": 0.316863, "comfort": 0.118531, "practicality": 0.22792}}</t>
+          <t>{"HVAC": {"energy_cost": 0.336451, "environmental": 0.32038, "comfort": 0.269486, "practicality": 0.073683}, "Appliance": {"energy_cost": 0.193182, "environmental": 0.465156, "comfort": 0.123615, "practicality": 0.218047}, "Shower": {"energy_cost": 0.335356, "environmental": 0.315611, "comfort": 0.122014, "practicality": 0.227019}}</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -690,22 +690,22 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.88422</v>
+        <v>0.88812</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9009</v>
+        <v>0.90388</v>
       </c>
       <c r="G7" t="n">
-        <v>0.93008</v>
+        <v>0.9313</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9859599999999998</v>
+        <v>0.9906599999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.23452</v>
+        <v>0.2393</v>
       </c>
       <c r="J7" t="n">
-        <v>0.88422</v>
+        <v>0.88812</v>
       </c>
     </row>
     <row r="8">
@@ -742,10 +742,10 @@
         <v>0.67798</v>
       </c>
       <c r="I8" t="n">
-        <v>0.29336</v>
+        <v>0.29542</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9122</v>
+        <v>0.91296</v>
       </c>
     </row>
     <row r="9">
@@ -770,22 +770,22 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.36548</v>
+        <v>0.36754</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3845999999999999</v>
+        <v>0.38564</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5518000000000001</v>
+        <v>0.5456199999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8194799999999999</v>
+        <v>0.8154</v>
       </c>
       <c r="I9" t="n">
-        <v>0.29336</v>
+        <v>0.29542</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9122</v>
+        <v>0.91296</v>
       </c>
     </row>
     <row r="10">
@@ -810,22 +810,22 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.9122</v>
+        <v>0.91296</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9224399999999999</v>
+        <v>0.92302</v>
       </c>
       <c r="G10" t="n">
-        <v>0.93244</v>
+        <v>0.9335800000000001</v>
       </c>
       <c r="H10" t="n">
         <v>0.9812799999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>0.29336</v>
+        <v>0.29542</v>
       </c>
       <c r="J10" t="n">
-        <v>0.9122</v>
+        <v>0.91296</v>
       </c>
     </row>
     <row r="11">
@@ -862,10 +862,10 @@
         <v>0.6882200000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>0.25368</v>
+        <v>0.25574</v>
       </c>
       <c r="J11" t="n">
-        <v>0.90906</v>
+        <v>0.9098200000000001</v>
       </c>
     </row>
     <row r="12">
@@ -890,22 +890,22 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.31966</v>
+        <v>0.32172</v>
       </c>
       <c r="F12" t="n">
-        <v>0.34616</v>
+        <v>0.34718</v>
       </c>
       <c r="G12" t="n">
-        <v>0.51384</v>
+        <v>0.5076799999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8</v>
+        <v>0.7959000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>0.25368</v>
+        <v>0.25574</v>
       </c>
       <c r="J12" t="n">
-        <v>0.90906</v>
+        <v>0.9098200000000001</v>
       </c>
     </row>
     <row r="13">
@@ -930,22 +930,22 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.90906</v>
+        <v>0.9098200000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>0.92012</v>
+        <v>0.9206800000000002</v>
       </c>
       <c r="G13" t="n">
-        <v>0.92078</v>
+        <v>0.9219200000000001</v>
       </c>
       <c r="H13" t="n">
         <v>0.9812799999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>0.25368</v>
+        <v>0.25574</v>
       </c>
       <c r="J13" t="n">
-        <v>0.90906</v>
+        <v>0.9098200000000001</v>
       </c>
     </row>
     <row r="14">
@@ -982,10 +982,10 @@
         <v>0.70974</v>
       </c>
       <c r="I14" t="n">
-        <v>0.13058</v>
+        <v>0.1142</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8827399999999999</v>
+        <v>0.8742000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -1010,22 +1010,22 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.24374</v>
+        <v>0.22736</v>
       </c>
       <c r="F15" t="n">
-        <v>0.26052</v>
+        <v>0.24254</v>
       </c>
       <c r="G15" t="n">
-        <v>0.46872</v>
+        <v>0.4615600000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7558999999999999</v>
+        <v>0.7507600000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>0.13058</v>
+        <v>0.1142</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8827399999999999</v>
+        <v>0.8742000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -1050,22 +1050,22 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.8827399999999999</v>
+        <v>0.8742000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9026999999999999</v>
+        <v>0.89688</v>
       </c>
       <c r="G16" t="n">
-        <v>0.91264</v>
+        <v>0.90564</v>
       </c>
       <c r="H16" t="n">
         <v>0.9836599999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>0.13058</v>
+        <v>0.1142</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8827399999999999</v>
+        <v>0.8742000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -1090,22 +1090,22 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.04072</v>
+        <v>0.04274</v>
       </c>
       <c r="F17" t="n">
-        <v>0.03793999999999999</v>
+        <v>0.04049999999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>0.34562</v>
+        <v>0.34668</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6748800000000001</v>
+        <v>0.679</v>
       </c>
       <c r="I17" t="n">
-        <v>0.23176</v>
+        <v>0.23726</v>
       </c>
       <c r="J17" t="n">
-        <v>0.88498</v>
+        <v>0.885</v>
       </c>
     </row>
     <row r="18">
@@ -1130,22 +1130,22 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.27248</v>
+        <v>0.28</v>
       </c>
       <c r="F18" t="n">
-        <v>0.28462</v>
+        <v>0.28974</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4892</v>
+        <v>0.49332</v>
       </c>
       <c r="H18" t="n">
-        <v>0.77846</v>
+        <v>0.77128</v>
       </c>
       <c r="I18" t="n">
-        <v>0.23176</v>
+        <v>0.23726</v>
       </c>
       <c r="J18" t="n">
-        <v>0.88498</v>
+        <v>0.885</v>
       </c>
     </row>
     <row r="19">
@@ -1170,22 +1170,22 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.88498</v>
+        <v>0.885</v>
       </c>
       <c r="F19" t="n">
-        <v>0.90266</v>
+        <v>0.9026799999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9289400000000001</v>
+        <v>0.92432</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9882799999999999</v>
+        <v>0.9929600000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>0.23176</v>
+        <v>0.23726</v>
       </c>
       <c r="J19" t="n">
-        <v>0.88498</v>
+        <v>0.885</v>
       </c>
     </row>
   </sheetData>

--- a/Analysis/Sensitivity_merec_entropy_arms_gptoss.xlsx
+++ b/Analysis/Sensitivity_merec_entropy_arms_gptoss.xlsx
@@ -961,7 +961,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Appliance": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Shower": {"energy_cost": 0.248, "environmental": 0.244, "comfort": 0.203, "practicality": 0.305}}</t>
+          <t>{"HVAC": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Appliance": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Shower": {"energy_cost": 0.251251, "environmental": 0.245245, "comfort": 0.203203, "practicality": 0.3003}}</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -970,22 +970,22 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.11316</v>
+        <v>0.10632</v>
       </c>
       <c r="F14" t="n">
-        <v>0.11998</v>
+        <v>0.11384</v>
       </c>
       <c r="G14" t="n">
-        <v>0.39076</v>
+        <v>0.38256</v>
       </c>
       <c r="H14" t="n">
-        <v>0.70974</v>
+        <v>0.7056600000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1142</v>
+        <v>0.12104</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8742000000000001</v>
+        <v>0.8718800000000002</v>
       </c>
     </row>
     <row r="15">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Appliance": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Shower": {"energy_cost": 0.248, "environmental": 0.244, "comfort": 0.203, "practicality": 0.305}}</t>
+          <t>{"HVAC": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Appliance": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Shower": {"energy_cost": 0.251251, "environmental": 0.245245, "comfort": 0.203203, "practicality": 0.3003}}</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1013,19 +1013,19 @@
         <v>0.22736</v>
       </c>
       <c r="F15" t="n">
-        <v>0.24254</v>
+        <v>0.24204</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4615600000000001</v>
+        <v>0.46462</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7507600000000001</v>
+        <v>0.74664</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1142</v>
+        <v>0.12104</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8742000000000001</v>
+        <v>0.8718800000000002</v>
       </c>
     </row>
     <row r="16">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Appliance": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Shower": {"energy_cost": 0.248, "environmental": 0.244, "comfort": 0.203, "practicality": 0.305}}</t>
+          <t>{"HVAC": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Appliance": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Shower": {"energy_cost": 0.251251, "environmental": 0.245245, "comfort": 0.203203, "practicality": 0.3003}}</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1050,22 +1050,22 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.8742000000000001</v>
+        <v>0.8718800000000002</v>
       </c>
       <c r="F16" t="n">
-        <v>0.89688</v>
+        <v>0.8951399999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>0.90564</v>
+        <v>0.9021399999999999</v>
       </c>
       <c r="H16" t="n">
         <v>0.9836599999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1142</v>
+        <v>0.12104</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8742000000000001</v>
+        <v>0.8718800000000002</v>
       </c>
     </row>
     <row r="17">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.336336, "environmental": 0.32032, "comfort": 0.269269, "practicality": 0.074074}, "Appliance": {"energy_cost": 0.193, "environmental": 0.465, "comfort": 0.124, "practicality": 0.218}, "Shower": {"energy_cost": 0.333666, "environmental": 0.313686, "comfort": 0.126873, "practicality": 0.225774}}</t>
+          <t>{"HVAC": {"energy_cost": 0.336336, "environmental": 0.32032, "comfort": 0.269269, "practicality": 0.074074}, "Appliance": {"energy_cost": 0.193, "environmental": 0.465, "comfort": 0.124, "practicality": 0.218}, "Shower": {"energy_cost": 0.335, "environmental": 0.316, "comfort": 0.122, "practicality": 0.227}}</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1093,19 +1093,19 @@
         <v>0.04274</v>
       </c>
       <c r="F17" t="n">
-        <v>0.04049999999999999</v>
+        <v>0.03948</v>
       </c>
       <c r="G17" t="n">
-        <v>0.34668</v>
+        <v>0.3477</v>
       </c>
       <c r="H17" t="n">
-        <v>0.679</v>
+        <v>0.6769400000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>0.23726</v>
+        <v>0.2393</v>
       </c>
       <c r="J17" t="n">
-        <v>0.885</v>
+        <v>0.88812</v>
       </c>
     </row>
     <row r="18">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.336336, "environmental": 0.32032, "comfort": 0.269269, "practicality": 0.074074}, "Appliance": {"energy_cost": 0.193, "environmental": 0.465, "comfort": 0.124, "practicality": 0.218}, "Shower": {"energy_cost": 0.333666, "environmental": 0.313686, "comfort": 0.126873, "practicality": 0.225774}}</t>
+          <t>{"HVAC": {"energy_cost": 0.336336, "environmental": 0.32032, "comfort": 0.269269, "practicality": 0.074074}, "Appliance": {"energy_cost": 0.193, "environmental": 0.465, "comfort": 0.124, "practicality": 0.218}, "Shower": {"energy_cost": 0.335, "environmental": 0.316, "comfort": 0.122, "practicality": 0.227}}</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1130,22 +1130,22 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.28</v>
+        <v>0.28204</v>
       </c>
       <c r="F18" t="n">
-        <v>0.28974</v>
+        <v>0.29128</v>
       </c>
       <c r="G18" t="n">
-        <v>0.49332</v>
+        <v>0.4964200000000001</v>
       </c>
       <c r="H18" t="n">
         <v>0.77128</v>
       </c>
       <c r="I18" t="n">
-        <v>0.23726</v>
+        <v>0.2393</v>
       </c>
       <c r="J18" t="n">
-        <v>0.885</v>
+        <v>0.88812</v>
       </c>
     </row>
     <row r="19">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.336336, "environmental": 0.32032, "comfort": 0.269269, "practicality": 0.074074}, "Appliance": {"energy_cost": 0.193, "environmental": 0.465, "comfort": 0.124, "practicality": 0.218}, "Shower": {"energy_cost": 0.333666, "environmental": 0.313686, "comfort": 0.126873, "practicality": 0.225774}}</t>
+          <t>{"HVAC": {"energy_cost": 0.336336, "environmental": 0.32032, "comfort": 0.269269, "practicality": 0.074074}, "Appliance": {"energy_cost": 0.193, "environmental": 0.465, "comfort": 0.124, "practicality": 0.218}, "Shower": {"energy_cost": 0.335, "environmental": 0.316, "comfort": 0.122, "practicality": 0.227}}</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1170,22 +1170,22 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.885</v>
+        <v>0.88812</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9026799999999999</v>
+        <v>0.90388</v>
       </c>
       <c r="G19" t="n">
-        <v>0.92432</v>
+        <v>0.9313</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9929600000000001</v>
+        <v>0.9906599999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>0.23726</v>
+        <v>0.2393</v>
       </c>
       <c r="J19" t="n">
-        <v>0.885</v>
+        <v>0.88812</v>
       </c>
     </row>
   </sheetData>
